--- a/Roles&permission.xlsx
+++ b/Roles&permission.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\skasi\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ecom\ecom_api_universal_new\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="54">
   <si>
     <t>Role</t>
   </si>
@@ -53,15 +53,6 @@
     <t>dashboard</t>
   </si>
   <si>
-    <t>"product.add"</t>
-  </si>
-  <si>
-    <t>"product.edit"</t>
-  </si>
-  <si>
-    <t>"product.view"</t>
-  </si>
-  <si>
     <t>sections</t>
   </si>
   <si>
@@ -183,6 +174,18 @@
   </si>
   <si>
     <t>shippingprovidersedit</t>
+  </si>
+  <si>
+    <t>contactsettings</t>
+  </si>
+  <si>
+    <t>product_section_view</t>
+  </si>
+  <si>
+    <t>whatsapp_agent</t>
+  </si>
+  <si>
+    <t>Hide Admin side</t>
   </si>
 </sst>
 </file>
@@ -507,7 +510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C72"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
@@ -521,6 +524,9 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -529,25 +535,19 @@
       <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="C3" s="1"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>11</v>
-      </c>
+      <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
@@ -561,7 +561,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -574,7 +574,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
         <v>5</v>
@@ -582,42 +582,42 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B22" t="s">
         <v>3</v>
@@ -640,7 +640,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -650,12 +650,12 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B30" t="s">
         <v>5</v>
@@ -663,12 +663,12 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B33" t="s">
         <v>5</v>
@@ -676,17 +676,17 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B37" t="s">
         <v>5</v>
@@ -694,22 +694,22 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B42" t="s">
         <v>5</v>
@@ -717,7 +717,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B44" t="s">
         <v>5</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B48" t="s">
         <v>5</v>
@@ -743,17 +743,17 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -768,75 +768,93 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B55" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B65" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B66" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B67" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B65" t="s">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B68" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B66" t="s">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B69" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B67" t="s">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B70" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B68" t="s">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
         <v>52</v>
+      </c>
+      <c r="B72" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Roles&permission.xlsx
+++ b/Roles&permission.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="58">
   <si>
     <t>Role</t>
   </si>
@@ -186,6 +186,18 @@
   </si>
   <si>
     <t>Hide Admin side</t>
+  </si>
+  <si>
+    <t>roles</t>
+  </si>
+  <si>
+    <t>manage</t>
+  </si>
+  <si>
+    <t>assign_roles</t>
+  </si>
+  <si>
+    <t>assign</t>
   </si>
 </sst>
 </file>
@@ -510,7 +522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C72"/>
+  <dimension ref="A1:C79"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
@@ -857,6 +869,37 @@
         <v>5</v>
       </c>
     </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>54</v>
+      </c>
+      <c r="B74" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B75" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B76" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>56</v>
+      </c>
+      <c r="B78" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B79" t="s">
+        <v>57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="261" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>

--- a/Roles&permission.xlsx
+++ b/Roles&permission.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ecom\ecom_api_universal_new\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ecom\new ecom version\ecom_api_universal_new\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54A1D735-2E14-4C59-9342-23A7601C3381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11865"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="58">
   <si>
     <t>Role</t>
   </si>
@@ -203,7 +204,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -521,15 +522,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C79"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C80"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.140625" customWidth="1"/>
+    <col min="1" max="1" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -540,7 +541,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -549,34 +550,34 @@
       </c>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="1"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="1"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -584,7 +585,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -592,42 +593,42 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>18</v>
       </c>
@@ -635,37 +636,37 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>21</v>
       </c>
@@ -673,12 +674,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>19</v>
       </c>
@@ -686,17 +687,17 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>25</v>
       </c>
@@ -704,22 +705,22 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>29</v>
       </c>
@@ -727,7 +728,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>30</v>
       </c>
@@ -735,17 +736,17 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>31</v>
       </c>
@@ -753,32 +754,32 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B50" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B52" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B53" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>35</v>
       </c>
@@ -786,117 +787,122 @@
         <v>36</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B56" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B57" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B58" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B59" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B60" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B62" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B64" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B65" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B66" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B67" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B68" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B69" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B70" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B71" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
         <v>52</v>
       </c>
-      <c r="B72" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+      <c r="B73" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
         <v>54</v>
       </c>
-      <c r="B74" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B76" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B76" t="s">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B77" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>56</v>
       </c>
-      <c r="B78" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B80" t="s">
         <v>57</v>
       </c>
     </row>
